--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="465">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -640,6 +640,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Timing.repeat.bounds[x]</t>
   </si>
   <si>
@@ -723,6 +726,26 @@
     <t>DR.2</t>
   </si>
   <si>
+    <t>Dosage.timing.repeat.bounds[x]:boundsDuration</t>
+  </si>
+  <si>
+    <t>boundsDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration
+</t>
+  </si>
+  <si>
+    <t>Dosage.timing.repeat.bounds[x]:boundsRange</t>
+  </si>
+  <si>
+    <t>boundsRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
     <t>Dosage.timing.repeat.count</t>
   </si>
   <si>
@@ -1017,9 +1040,6 @@
     <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>.outboundRelationship[typeCode=PRCN].target[classCode=OBS, moodCode=EVN, code="as needed"].value=boolean or codable concept</t>
   </si>
   <si>
@@ -1184,10 +1204,6 @@
   </si>
   <si>
     <t>doseRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range
-</t>
   </si>
   <si>
     <t>Dosierungsspanne wird mit low und high angegeben, z.B. 5-10 mg.</t>
@@ -1423,6 +1439,10 @@
   </si>
   <si>
     <t>The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>not supported</t>
@@ -1758,7 +1778,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL68"/>
+  <dimension ref="A1:AL70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="true" bestFit="true"/>
@@ -4364,10 +4384,10 @@
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>94</v>
+        <v>198</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -4382,7 +4402,7 @@
         <v>124</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
@@ -4390,13 +4410,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>20</v>
@@ -4418,7 +4438,7 @@
         <v>127</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>195</v>
@@ -4475,7 +4495,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -4490,7 +4510,7 @@
         <v>124</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
@@ -4498,10 +4518,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4604,10 +4624,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4712,10 +4732,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4741,13 +4761,13 @@
         <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4797,7 +4817,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4806,24 +4826,24 @@
         <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4849,20 +4869,20 @@
         <v>171</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q29" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="R29" t="s" s="2">
         <v>20</v>
@@ -4907,7 +4927,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4916,26 +4936,28 @@
         <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>20</v>
       </c>
@@ -4956,20 +4978,16 @@
         <v>127</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5017,7 +5035,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -5032,7 +5050,7 @@
         <v>124</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
@@ -5040,12 +5058,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5066,13 +5086,13 @@
         <v>127</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5123,7 +5143,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -5138,7 +5158,7 @@
         <v>124</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
@@ -5146,10 +5166,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5172,19 +5192,19 @@
         <v>127</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5233,7 +5253,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -5248,7 +5268,7 @@
         <v>124</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>20</v>
@@ -5256,10 +5276,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5282,20 +5302,16 @@
         <v>127</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O33" t="s" s="2">
         <v>242</v>
       </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5343,7 +5359,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -5358,7 +5374,7 @@
         <v>124</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>20</v>
@@ -5366,10 +5382,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5392,16 +5408,20 @@
         <v>127</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5425,13 +5445,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>254</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5449,7 +5469,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5464,7 +5484,7 @@
         <v>124</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
@@ -5472,10 +5492,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5483,7 +5503,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>82</v>
@@ -5498,22 +5518,24 @@
         <v>127</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q35" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5557,7 +5579,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5572,7 +5594,7 @@
         <v>124</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
@@ -5580,10 +5602,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5594,7 +5616,7 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5606,13 +5628,13 @@
         <v>127</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5639,13 +5661,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5663,7 +5685,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5678,18 +5700,18 @@
         <v>124</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5703,7 +5725,7 @@
         <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
@@ -5712,20 +5734,22 @@
         <v>127</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q37" s="2"/>
+      <c r="Q37" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="R37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5769,7 +5793,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5784,7 +5808,7 @@
         <v>124</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -5792,10 +5816,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5818,13 +5842,13 @@
         <v>127</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5875,7 +5899,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5890,18 +5914,18 @@
         <v>124</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5915,7 +5939,7 @@
         <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -5924,13 +5948,13 @@
         <v>127</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5957,11 +5981,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -5979,7 +6005,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5994,7 +6020,7 @@
         <v>124</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -6002,10 +6028,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6016,7 +6042,7 @@
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6028,17 +6054,15 @@
         <v>127</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6063,11 +6087,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y40" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>283</v>
+        <v>20</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6085,13 +6111,13 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
@@ -6100,7 +6126,7 @@
         <v>124</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -6108,10 +6134,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6119,10 +6145,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6134,17 +6160,15 @@
         <v>127</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6169,13 +6193,11 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>20</v>
+        <v>284</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6193,13 +6215,13 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
@@ -6208,18 +6230,18 @@
         <v>124</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>87</v>
+        <v>263</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6227,13 +6249,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
@@ -6242,20 +6264,18 @@
         <v>127</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6283,7 +6303,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6301,7 +6321,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6316,18 +6336,18 @@
         <v>124</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>298</v>
+        <v>87</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6341,7 +6361,7 @@
         <v>74</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
@@ -6350,15 +6370,17 @@
         <v>127</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6407,13 +6429,13 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
@@ -6422,18 +6444,18 @@
         <v>124</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>304</v>
+        <v>87</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6441,13 +6463,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
@@ -6456,18 +6478,20 @@
         <v>127</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -6491,13 +6515,11 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6515,13 +6537,13 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
@@ -6530,18 +6552,18 @@
         <v>124</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6552,10 +6574,10 @@
         <v>74</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
@@ -6564,17 +6586,15 @@
         <v>127</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6599,29 +6619,31 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>319</v>
+        <v>20</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>320</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AC45" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6636,22 +6658,20 @@
         <v>124</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>20</v>
       </c>
@@ -6663,7 +6683,7 @@
         <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
@@ -6672,16 +6692,16 @@
         <v>127</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6707,13 +6727,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>20</v>
+        <v>317</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -6731,7 +6751,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6746,22 +6766,20 @@
         <v>124</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>20</v>
       </c>
@@ -6770,7 +6788,7 @@
         <v>74</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -6782,16 +6800,16 @@
         <v>127</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>116</v>
+        <v>322</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6820,28 +6838,26 @@
         <v>150</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -6856,20 +6872,22 @@
         <v>124</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
       </c>
@@ -6881,7 +6899,7 @@
         <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>20</v>
@@ -6890,20 +6908,18 @@
         <v>127</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>116</v>
+        <v>322</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -6927,13 +6943,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -6951,7 +6967,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -6966,20 +6982,22 @@
         <v>124</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>20</v>
       </c>
@@ -6988,10 +7006,10 @@
         <v>74</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
@@ -7003,15 +7021,15 @@
         <v>116</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7035,11 +7053,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7057,7 +7077,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -7072,18 +7092,18 @@
         <v>124</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>345</v>
+        <v>329</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7097,7 +7117,7 @@
         <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
@@ -7109,16 +7129,16 @@
         <v>116</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7146,10 +7166,10 @@
         <v>150</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7167,7 +7187,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
@@ -7182,18 +7202,18 @@
         <v>124</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7216,16 +7236,18 @@
         <v>127</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>178</v>
+        <v>116</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
@@ -7249,13 +7271,11 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7273,13 +7293,13 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
@@ -7288,18 +7308,18 @@
         <v>124</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7313,25 +7333,29 @@
         <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>84</v>
+        <v>353</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -7355,13 +7379,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>20</v>
+        <v>357</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7379,7 +7403,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>86</v>
+        <v>352</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7391,54 +7415,52 @@
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>87</v>
+        <v>359</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>20</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>167</v>
+        <v>362</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7475,19 +7497,19 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>95</v>
+        <v>361</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7499,21 +7521,21 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7533,21 +7555,19 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>362</v>
+        <v>84</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>363</v>
+        <v>85</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>364</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -7571,13 +7591,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>365</v>
+        <v>20</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -7595,7 +7615,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>361</v>
+        <v>86</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
@@ -7607,32 +7627,32 @@
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>367</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -7641,23 +7661,21 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>369</v>
+        <v>89</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>370</v>
+        <v>167</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>371</v>
+        <v>168</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
       </c>
@@ -7693,47 +7711,47 @@
         <v>20</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>321</v>
+        <v>94</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>95</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>353</v>
+        <v>87</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>374</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>20</v>
       </c>
@@ -7745,7 +7763,7 @@
         <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>20</v>
@@ -7754,19 +7772,17 @@
         <v>127</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>377</v>
+        <v>116</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -7791,13 +7807,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>20</v>
+        <v>372</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -7815,7 +7831,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7830,22 +7846,20 @@
         <v>124</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
         <v>374</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="B57" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>20</v>
       </c>
@@ -7857,7 +7871,7 @@
         <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>20</v>
@@ -7866,19 +7880,19 @@
         <v>127</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -7915,19 +7929,17 @@
         <v>20</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -7942,20 +7954,22 @@
         <v>124</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>374</v>
       </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C58" s="2"/>
+      <c r="C58" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>20</v>
       </c>
@@ -7967,25 +7981,29 @@
         <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>83</v>
+        <v>231</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>84</v>
+        <v>383</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -8033,7 +8051,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>86</v>
+        <v>374</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -8045,55 +8063,59 @@
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>87</v>
+        <v>359</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="B59" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>89</v>
+        <v>386</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>167</v>
+        <v>387</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>168</v>
+        <v>377</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
       </c>
@@ -8129,45 +8151,45 @@
         <v>20</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>95</v>
+        <v>374</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>87</v>
+        <v>359</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8187,23 +8209,19 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -8251,7 +8269,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>393</v>
+        <v>86</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -8263,61 +8281,59 @@
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>394</v>
+        <v>87</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>395</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>398</v>
+        <v>167</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q61" t="s" s="2">
-        <v>401</v>
-      </c>
+      <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
         <v>20</v>
       </c>
@@ -8337,57 +8353,57 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>402</v>
+        <v>20</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>403</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>404</v>
+        <v>95</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>405</v>
+        <v>87</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>406</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8410,17 +8426,19 @@
         <v>127</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>83</v>
+        <v>245</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="O62" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -8445,11 +8463,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -8467,7 +8487,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>74</v>
@@ -8482,18 +8502,18 @@
         <v>124</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>415</v>
+        <v>400</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8504,34 +8524,36 @@
         <v>74</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>127</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="R63" t="s" s="2">
         <v>20</v>
       </c>
@@ -8551,13 +8573,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>20</v>
+        <v>407</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>20</v>
+        <v>408</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -8575,7 +8597,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
@@ -8584,24 +8606,24 @@
         <v>82</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>422</v>
+        <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8624,19 +8646,17 @@
         <v>127</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>250</v>
+        <v>83</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -8661,13 +8681,11 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>20</v>
+        <v>417</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -8685,7 +8703,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>74</v>
@@ -8700,18 +8718,18 @@
         <v>124</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8734,19 +8752,17 @@
         <v>127</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>433</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -8795,7 +8811,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
@@ -8804,24 +8820,24 @@
         <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>20</v>
+        <v>427</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>439</v>
+        <v>420</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8844,19 +8860,19 @@
         <v>127</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>441</v>
+        <v>257</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -8905,7 +8921,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
@@ -8920,18 +8936,18 @@
         <v>124</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>447</v>
+        <v>420</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8954,19 +8970,19 @@
         <v>127</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -9015,7 +9031,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
@@ -9030,18 +9046,18 @@
         <v>124</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>20</v>
+        <v>444</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9064,17 +9080,19 @@
         <v>127</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L68" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9123,7 +9141,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
@@ -9138,14 +9156,232 @@
         <v>124</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K69" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="L69" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL68">
+  <autoFilter ref="A1:AL70">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9155,7 +9391,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI67">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$81</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="525">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1103,13 +1103,194 @@
     <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
+    <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>.routeCode</t>
+  </si>
+  <si>
+    <t>RXR-1</t>
+  </si>
+  <si>
+    <t>Dosage.route.id</t>
+  </si>
+  <si>
+    <t>Dosage.route.extension</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.id</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.extension</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
     <t>https://termgit.elga.gv.at/CodeSystem/medikationartanwendung</t>
   </si>
   <si>
-    <t>.routeCode</t>
-  </si>
-  <si>
-    <t>RXR-1</t>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Dosage.route.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -1778,7 +1959,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL70"/>
+  <dimension ref="A1:AL81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="true" bestFit="true"/>
@@ -1817,7 +1998,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="109.8359375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7271,11 +7452,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7308,18 +7491,18 @@
         <v>124</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7333,29 +7516,25 @@
         <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>353</v>
+        <v>84</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -7379,13 +7558,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>357</v>
+        <v>20</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7403,7 +7582,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>352</v>
+        <v>86</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7415,52 +7594,54 @@
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>359</v>
+        <v>87</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>362</v>
+        <v>167</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7497,19 +7678,19 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>361</v>
+        <v>95</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7521,21 +7702,21 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>364</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7546,7 +7727,7 @@
         <v>74</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -7555,19 +7736,23 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -7615,44 +7800,44 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>86</v>
+        <v>361</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>87</v>
+        <v>362</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>20</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -7664,17 +7849,15 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -7711,31 +7894,31 @@
         <v>20</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>87</v>
@@ -7746,21 +7929,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -7769,21 +7952,21 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>368</v>
+        <v>167</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>20</v>
       </c>
@@ -7807,57 +7990,57 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>367</v>
+        <v>95</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7880,19 +8063,19 @@
         <v>127</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>375</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -7902,7 +8085,7 @@
         <v>20</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>20</v>
@@ -7929,17 +8112,19 @@
         <v>20</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AC57" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -7954,22 +8139,20 @@
         <v>124</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>20</v>
       </c>
@@ -7981,7 +8164,7 @@
         <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
@@ -7990,10 +8173,10 @@
         <v>127</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="M58" t="s" s="2">
         <v>377</v>
@@ -8001,9 +8184,7 @@
       <c r="N58" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>379</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -8051,7 +8232,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -8066,22 +8247,20 @@
         <v>124</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>20</v>
       </c>
@@ -8093,7 +8272,7 @@
         <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>20</v>
@@ -8102,19 +8281,17 @@
         <v>127</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>386</v>
+        <v>257</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8163,7 +8340,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
@@ -8178,15 +8355,15 @@
         <v>124</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>389</v>
@@ -8209,19 +8386,21 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>85</v>
+        <v>391</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -8269,7 +8448,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>86</v>
+        <v>393</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -8281,32 +8460,32 @@
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>87</v>
+        <v>394</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>20</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8315,21 +8494,23 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>89</v>
+        <v>322</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>167</v>
+        <v>397</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>168</v>
+        <v>398</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
       </c>
@@ -8365,45 +8546,45 @@
         <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>95</v>
+        <v>401</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>20</v>
+        <v>403</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8426,19 +8607,19 @@
         <v>127</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>245</v>
+        <v>83</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -8487,7 +8668,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>74</v>
@@ -8502,18 +8683,18 @@
         <v>124</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8524,36 +8705,36 @@
         <v>74</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>127</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>257</v>
+        <v>116</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q63" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
         <v>20</v>
       </c>
@@ -8573,13 +8754,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -8597,7 +8778,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
@@ -8612,18 +8793,18 @@
         <v>124</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8637,7 +8818,7 @@
         <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>20</v>
@@ -8646,18 +8827,16 @@
         <v>127</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>416</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>20</v>
       </c>
@@ -8681,11 +8860,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>417</v>
+        <v>20</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -8703,13 +8884,13 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
@@ -8718,18 +8899,18 @@
         <v>124</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8749,21 +8930,19 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>424</v>
+        <v>85</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>425</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>20</v>
       </c>
@@ -8811,7 +8990,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>426</v>
+        <v>86</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
@@ -8820,35 +8999,35 @@
         <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>427</v>
+        <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>428</v>
+        <v>87</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>420</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -8857,23 +9036,21 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>257</v>
+        <v>89</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>431</v>
+        <v>167</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>20</v>
       </c>
@@ -8909,45 +9086,45 @@
         <v>20</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>435</v>
+        <v>95</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>436</v>
+        <v>87</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>420</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8970,19 +9147,17 @@
         <v>127</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>438</v>
+        <v>116</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -9007,13 +9182,13 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>20</v>
+        <v>431</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -9031,7 +9206,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
@@ -9046,18 +9221,18 @@
         <v>124</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>443</v>
+        <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>444</v>
+        <v>433</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9080,19 +9255,19 @@
         <v>127</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9129,19 +9304,17 @@
         <v>20</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
@@ -9156,20 +9329,22 @@
         <v>124</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>452</v>
+        <v>440</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>20</v>
       </c>
@@ -9181,7 +9356,7 @@
         <v>82</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>20</v>
@@ -9190,19 +9365,19 @@
         <v>127</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>454</v>
+        <v>231</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9251,7 +9426,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
@@ -9263,23 +9438,25 @@
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>459</v>
+        <v>124</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>460</v>
+        <v>419</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>20</v>
+        <v>440</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>20</v>
       </c>
@@ -9291,7 +9468,7 @@
         <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>20</v>
@@ -9300,17 +9477,19 @@
         <v>127</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="O70" t="s" s="2">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -9359,29 +9538,1225 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AG70" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AL70" t="s" s="2">
+      <c r="B74" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q74" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="R74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="Y75" s="2"/>
+      <c r="Z75" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AL81" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL70">
+  <autoFilter ref="A1:AL81">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9391,7 +10766,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI80">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7163,7 +7163,7 @@
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>101</v>
@@ -11273,7 +11273,7 @@
         <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>101</v>
@@ -11383,7 +11383,7 @@
         <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>101</v>
@@ -11489,7 +11489,7 @@
         <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>101</v>
@@ -11599,7 +11599,7 @@
         <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>101</v>
@@ -11709,7 +11709,7 @@
         <v>76</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>101</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1951,7 +1951,7 @@
     <t>TODO</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationmengenart</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.dose[x]:doseQuantity.id</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -678,7 +678,7 @@
     <t>Dosage.text</t>
   </si>
   <si>
-    <t>Freitext-Dosierungsanweisung, wenn keine strukturierte Angabe möglich ist.</t>
+    <t>Textdarstellung der Dosierung: bei strukturierter Dosierung durch die Fachanwendung generiert, sonst Freitext-Dosierungsanweisung (wenn keine strukturierte Angabe möglich ist).</t>
   </si>
   <si>
     <t>Free text dosage instructions e.g. SIG.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8365" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8364" uniqueCount="793">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -294,6 +294,9 @@
     <t>Dosage.extension</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
@@ -325,9 +328,6 @@
   </si>
   <si>
     <t>DosageCategory</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-dosage-category}
@@ -3150,7 +3150,7 @@
         <v>77</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -3159,13 +3159,13 @@
         <v>21</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -3204,19 +3204,19 @@
         <v>21</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>76</v>
@@ -3228,7 +3228,7 @@
         <v>21</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>21</v>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>21</v>
@@ -3258,7 +3258,7 @@
         <v>77</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>21</v>
@@ -3324,7 +3324,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -3336,7 +3336,7 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
@@ -3479,13 +3479,13 @@
         <v>21</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -3524,19 +3524,19 @@
         <v>21</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -3548,7 +3548,7 @@
         <v>21</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>21</v>
@@ -3576,7 +3576,7 @@
         <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
@@ -3684,7 +3684,7 @@
         <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>21</v>
@@ -3905,7 +3905,7 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>132</v>
@@ -3952,19 +3952,19 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3976,7 +3976,7 @@
         <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>89</v>
@@ -4004,13 +4004,13 @@
         <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
         <v>137</v>
@@ -4229,7 +4229,7 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>132</v>
@@ -4276,19 +4276,19 @@
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -4300,7 +4300,7 @@
         <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>89</v>
@@ -4328,13 +4328,13 @@
         <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
         <v>110</v>
@@ -4438,13 +4438,13 @@
         <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>85</v>
@@ -4546,13 +4546,13 @@
         <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>169</v>
@@ -4654,13 +4654,13 @@
         <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>85</v>
@@ -4768,7 +4768,7 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
         <v>187</v>
@@ -4878,7 +4878,7 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>85</v>
@@ -4985,19 +4985,19 @@
         <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5060,7 +5060,7 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
@@ -5088,13 +5088,13 @@
         <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>208</v>
@@ -5196,13 +5196,13 @@
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>85</v>
@@ -5304,13 +5304,13 @@
         <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>119</v>
@@ -5529,7 +5529,7 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>132</v>
@@ -5576,19 +5576,19 @@
         <v>21</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5600,7 +5600,7 @@
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>89</v>
@@ -5628,13 +5628,13 @@
         <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>137</v>
@@ -5853,7 +5853,7 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>132</v>
@@ -5900,19 +5900,19 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5924,7 +5924,7 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>89</v>
@@ -5952,13 +5952,13 @@
         <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>110</v>
@@ -6062,13 +6062,13 @@
         <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>85</v>
@@ -6170,13 +6170,13 @@
         <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>169</v>
@@ -6278,13 +6278,13 @@
         <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>85</v>
@@ -6392,7 +6392,7 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>187</v>
@@ -6502,7 +6502,7 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>85</v>
@@ -6606,13 +6606,13 @@
         <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>85</v>
@@ -6712,13 +6712,13 @@
         <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>243</v>
@@ -6937,7 +6937,7 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>132</v>
@@ -6984,19 +6984,19 @@
         <v>21</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -7008,7 +7008,7 @@
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>89</v>
@@ -7039,19 +7039,19 @@
         <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>205</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7114,7 +7114,7 @@
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
@@ -7142,13 +7142,13 @@
         <v>76</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>253</v>
@@ -7250,13 +7250,13 @@
         <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>260</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7464,7 +7464,7 @@
         <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -7473,17 +7473,15 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7520,19 +7518,19 @@
         <v>21</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7544,10 +7542,10 @@
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -7574,7 +7572,7 @@
         <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -7642,7 +7640,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7654,7 +7652,7 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7682,13 +7680,13 @@
         <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>276</v>
@@ -7788,13 +7786,13 @@
         <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>285</v>
@@ -8009,7 +8007,7 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>132</v>
@@ -8056,19 +8054,19 @@
         <v>21</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -8080,7 +8078,7 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>89</v>
@@ -8108,13 +8106,13 @@
         <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>253</v>
@@ -8216,13 +8214,13 @@
         <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>253</v>
@@ -8328,13 +8326,13 @@
         <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>310</v>
@@ -8549,7 +8547,7 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>132</v>
@@ -8596,19 +8594,19 @@
         <v>21</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8620,7 +8618,7 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>89</v>
@@ -8648,13 +8646,13 @@
         <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>315</v>
@@ -8761,10 +8759,10 @@
         <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>169</v>
@@ -8868,13 +8866,13 @@
         <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>85</v>
@@ -8976,13 +8974,13 @@
         <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>110</v>
@@ -9084,13 +9082,13 @@
         <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>169</v>
@@ -9196,13 +9194,13 @@
         <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>359</v>
@@ -9417,7 +9415,7 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>132</v>
@@ -9464,19 +9462,19 @@
         <v>21</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9488,7 +9486,7 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>89</v>
@@ -9516,13 +9514,13 @@
         <v>84</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>364</v>
@@ -9739,7 +9737,7 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>132</v>
@@ -9786,19 +9784,19 @@
         <v>21</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9810,7 +9808,7 @@
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>89</v>
@@ -9838,13 +9836,13 @@
         <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>315</v>
@@ -9951,10 +9949,10 @@
         <v>21</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>169</v>
@@ -10058,13 +10056,13 @@
         <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>85</v>
@@ -10166,13 +10164,13 @@
         <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>110</v>
@@ -10274,13 +10272,13 @@
         <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>169</v>
@@ -10384,13 +10382,13 @@
         <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>364</v>
@@ -10607,7 +10605,7 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>132</v>
@@ -10654,19 +10652,19 @@
         <v>21</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10678,7 +10676,7 @@
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>89</v>
@@ -10706,13 +10704,13 @@
         <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>315</v>
@@ -10819,10 +10817,10 @@
         <v>21</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>169</v>
@@ -10926,13 +10924,13 @@
         <v>84</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>85</v>
@@ -11034,13 +11032,13 @@
         <v>84</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>110</v>
@@ -11142,13 +11140,13 @@
         <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>169</v>
@@ -11252,13 +11250,13 @@
         <v>76</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>408</v>
@@ -11362,13 +11360,13 @@
         <v>76</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>408</v>
@@ -11468,13 +11466,13 @@
         <v>76</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>315</v>
@@ -11578,13 +11576,13 @@
         <v>76</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>315</v>
@@ -11688,13 +11686,13 @@
         <v>76</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>169</v>
@@ -11794,13 +11792,13 @@
         <v>84</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>408</v>
@@ -11908,7 +11906,7 @@
         <v>21</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>408</v>
@@ -12008,13 +12006,13 @@
         <v>84</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>315</v>
@@ -12114,13 +12112,13 @@
         <v>76</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>315</v>
@@ -12220,13 +12218,13 @@
         <v>84</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>169</v>
@@ -12324,13 +12322,13 @@
         <v>77</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>169</v>
@@ -12430,13 +12428,13 @@
         <v>76</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>466</v>
@@ -12538,13 +12536,13 @@
         <v>77</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>169</v>
@@ -12646,13 +12644,13 @@
         <v>76</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>480</v>
@@ -12758,7 +12756,7 @@
         <v>21</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>119</v>
@@ -12860,13 +12858,13 @@
         <v>84</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>187</v>
@@ -12968,13 +12966,13 @@
         <v>84</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>119</v>
@@ -13193,7 +13191,7 @@
         <v>21</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>132</v>
@@ -13240,19 +13238,19 @@
         <v>21</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13264,7 +13262,7 @@
         <v>21</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>89</v>
@@ -13292,13 +13290,13 @@
         <v>84</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>137</v>
@@ -13517,7 +13515,7 @@
         <v>21</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>132</v>
@@ -13564,19 +13562,19 @@
         <v>21</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13588,7 +13586,7 @@
         <v>21</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>89</v>
@@ -13616,13 +13614,13 @@
         <v>84</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>110</v>
@@ -13726,13 +13724,13 @@
         <v>84</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
         <v>85</v>
@@ -13834,13 +13832,13 @@
         <v>84</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
         <v>169</v>
@@ -13942,13 +13940,13 @@
         <v>84</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>85</v>
@@ -14056,7 +14054,7 @@
         <v>21</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>187</v>
@@ -14166,7 +14164,7 @@
         <v>21</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>85</v>
@@ -14270,13 +14268,13 @@
         <v>84</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
         <v>119</v>
@@ -14493,7 +14491,7 @@
         <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>132</v>
@@ -14540,19 +14538,19 @@
         <v>21</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14564,7 +14562,7 @@
         <v>21</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>89</v>
@@ -14592,13 +14590,13 @@
         <v>84</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
         <v>137</v>
@@ -14817,7 +14815,7 @@
         <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>132</v>
@@ -14864,19 +14862,19 @@
         <v>21</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14888,7 +14886,7 @@
         <v>21</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>89</v>
@@ -14916,13 +14914,13 @@
         <v>84</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
         <v>110</v>
@@ -15026,13 +15024,13 @@
         <v>84</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
         <v>85</v>
@@ -15134,13 +15132,13 @@
         <v>84</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>169</v>
@@ -15242,13 +15240,13 @@
         <v>84</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>85</v>
@@ -15356,7 +15354,7 @@
         <v>21</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
         <v>187</v>
@@ -15466,7 +15464,7 @@
         <v>21</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
         <v>85</v>
@@ -15570,13 +15568,13 @@
         <v>84</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>119</v>
@@ -15795,7 +15793,7 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L121" t="s" s="2">
         <v>132</v>
@@ -15842,19 +15840,19 @@
         <v>21</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -15866,7 +15864,7 @@
         <v>21</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>89</v>
@@ -15894,13 +15892,13 @@
         <v>84</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
         <v>137</v>
@@ -16119,7 +16117,7 @@
         <v>21</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L124" t="s" s="2">
         <v>132</v>
@@ -16166,19 +16164,19 @@
         <v>21</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -16190,7 +16188,7 @@
         <v>21</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>89</v>
@@ -16218,13 +16216,13 @@
         <v>84</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
         <v>110</v>
@@ -16328,13 +16326,13 @@
         <v>84</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
         <v>85</v>
@@ -16436,13 +16434,13 @@
         <v>84</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
         <v>169</v>
@@ -16544,13 +16542,13 @@
         <v>84</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
         <v>85</v>
@@ -16658,7 +16656,7 @@
         <v>21</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
         <v>187</v>
@@ -16768,7 +16766,7 @@
         <v>21</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
         <v>85</v>
@@ -16872,13 +16870,13 @@
         <v>84</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>260</v>
@@ -17093,7 +17091,7 @@
         <v>21</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L133" t="s" s="2">
         <v>132</v>
@@ -17140,19 +17138,19 @@
         <v>21</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17164,7 +17162,7 @@
         <v>21</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>89</v>
@@ -17198,7 +17196,7 @@
         <v>21</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K134" t="s" s="2">
         <v>119</v>
@@ -17300,13 +17298,13 @@
         <v>84</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K135" t="s" s="2">
         <v>574</v>
@@ -17410,13 +17408,13 @@
         <v>84</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
         <v>359</v>
@@ -17635,7 +17633,7 @@
         <v>21</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L138" t="s" s="2">
         <v>132</v>
@@ -17682,19 +17680,19 @@
         <v>21</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -17706,7 +17704,7 @@
         <v>21</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>89</v>
@@ -17734,13 +17732,13 @@
         <v>84</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
         <v>364</v>
@@ -17957,7 +17955,7 @@
         <v>21</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L141" t="s" s="2">
         <v>132</v>
@@ -18004,19 +18002,19 @@
         <v>21</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18028,7 +18026,7 @@
         <v>21</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>89</v>
@@ -18056,13 +18054,13 @@
         <v>84</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
         <v>315</v>
@@ -18169,10 +18167,10 @@
         <v>21</v>
       </c>
       <c r="I143" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
         <v>169</v>
@@ -18276,13 +18274,13 @@
         <v>84</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K144" t="s" s="2">
         <v>85</v>
@@ -18384,13 +18382,13 @@
         <v>84</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K145" t="s" s="2">
         <v>110</v>
@@ -18492,13 +18490,13 @@
         <v>84</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
         <v>169</v>
@@ -18602,13 +18600,13 @@
         <v>84</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K147" t="s" s="2">
         <v>364</v>
@@ -18825,7 +18823,7 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>132</v>
@@ -18872,19 +18870,19 @@
         <v>21</v>
       </c>
       <c r="AB149" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC149" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD149" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE149" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>76</v>
@@ -18896,7 +18894,7 @@
         <v>21</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>89</v>
@@ -18924,13 +18922,13 @@
         <v>84</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
         <v>315</v>
@@ -19037,10 +19035,10 @@
         <v>21</v>
       </c>
       <c r="I151" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
         <v>169</v>
@@ -19144,13 +19142,13 @@
         <v>84</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K152" t="s" s="2">
         <v>85</v>
@@ -19252,13 +19250,13 @@
         <v>84</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K153" t="s" s="2">
         <v>110</v>
@@ -19360,13 +19358,13 @@
         <v>84</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K154" t="s" s="2">
         <v>169</v>
@@ -19472,13 +19470,13 @@
         <v>84</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I155" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
         <v>622</v>
@@ -19695,7 +19693,7 @@
         <v>21</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L157" t="s" s="2">
         <v>132</v>
@@ -19742,19 +19740,19 @@
         <v>21</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -19766,7 +19764,7 @@
         <v>21</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>89</v>
@@ -19794,13 +19792,13 @@
         <v>84</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K158" t="s" s="2">
         <v>315</v>
@@ -19907,10 +19905,10 @@
         <v>21</v>
       </c>
       <c r="I159" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K159" t="s" s="2">
         <v>169</v>
@@ -20014,13 +20012,13 @@
         <v>84</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K160" t="s" s="2">
         <v>85</v>
@@ -20122,13 +20120,13 @@
         <v>84</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K161" t="s" s="2">
         <v>110</v>
@@ -20230,13 +20228,13 @@
         <v>84</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K162" t="s" s="2">
         <v>169</v>
@@ -20340,13 +20338,13 @@
         <v>84</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
         <v>638</v>
@@ -20450,13 +20448,13 @@
         <v>84</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
         <v>622</v>
@@ -20675,7 +20673,7 @@
         <v>21</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>132</v>
@@ -20722,19 +20720,19 @@
         <v>21</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>76</v>
@@ -20746,7 +20744,7 @@
         <v>21</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>89</v>
@@ -20774,13 +20772,13 @@
         <v>84</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K167" t="s" s="2">
         <v>315</v>
@@ -20887,10 +20885,10 @@
         <v>21</v>
       </c>
       <c r="I168" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
         <v>169</v>
@@ -20994,13 +20992,13 @@
         <v>84</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K169" t="s" s="2">
         <v>85</v>
@@ -21102,13 +21100,13 @@
         <v>84</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K170" t="s" s="2">
         <v>110</v>
@@ -21210,13 +21208,13 @@
         <v>84</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K171" t="s" s="2">
         <v>169</v>
@@ -21322,13 +21320,13 @@
         <v>84</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
         <v>359</v>
@@ -21547,7 +21545,7 @@
         <v>21</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L174" t="s" s="2">
         <v>132</v>
@@ -21594,19 +21592,19 @@
         <v>21</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC174" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD174" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE174" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>76</v>
@@ -21618,7 +21616,7 @@
         <v>21</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>89</v>
@@ -21646,13 +21644,13 @@
         <v>84</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I175" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J175" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K175" t="s" s="2">
         <v>364</v>
@@ -21869,7 +21867,7 @@
         <v>21</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L177" t="s" s="2">
         <v>132</v>
@@ -21916,19 +21914,19 @@
         <v>21</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC177" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD177" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>76</v>
@@ -21940,7 +21938,7 @@
         <v>21</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>89</v>
@@ -21968,13 +21966,13 @@
         <v>84</v>
       </c>
       <c r="H178" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K178" t="s" s="2">
         <v>315</v>
@@ -22081,10 +22079,10 @@
         <v>21</v>
       </c>
       <c r="I179" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K179" t="s" s="2">
         <v>169</v>
@@ -22188,13 +22186,13 @@
         <v>84</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K180" t="s" s="2">
         <v>85</v>
@@ -22296,13 +22294,13 @@
         <v>84</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K181" t="s" s="2">
         <v>110</v>
@@ -22404,13 +22402,13 @@
         <v>84</v>
       </c>
       <c r="H182" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I182" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K182" t="s" s="2">
         <v>169</v>
@@ -22514,13 +22512,13 @@
         <v>84</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K183" t="s" s="2">
         <v>364</v>
@@ -22737,7 +22735,7 @@
         <v>21</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L185" t="s" s="2">
         <v>132</v>
@@ -22784,19 +22782,19 @@
         <v>21</v>
       </c>
       <c r="AB185" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC185" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD185" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE185" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>76</v>
@@ -22808,7 +22806,7 @@
         <v>21</v>
       </c>
       <c r="AJ185" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK185" t="s" s="2">
         <v>89</v>
@@ -22836,13 +22834,13 @@
         <v>84</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I186" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K186" t="s" s="2">
         <v>315</v>
@@ -22949,10 +22947,10 @@
         <v>21</v>
       </c>
       <c r="I187" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K187" t="s" s="2">
         <v>169</v>
@@ -23056,13 +23054,13 @@
         <v>84</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K188" t="s" s="2">
         <v>85</v>
@@ -23164,13 +23162,13 @@
         <v>84</v>
       </c>
       <c r="H189" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I189" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J189" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K189" t="s" s="2">
         <v>110</v>
@@ -23272,13 +23270,13 @@
         <v>84</v>
       </c>
       <c r="H190" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I190" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J190" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K190" t="s" s="2">
         <v>169</v>
@@ -23384,13 +23382,13 @@
         <v>84</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J191" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K191" t="s" s="2">
         <v>700</v>
@@ -23609,7 +23607,7 @@
         <v>21</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L193" t="s" s="2">
         <v>132</v>
@@ -23656,19 +23654,19 @@
         <v>21</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>76</v>
@@ -23680,7 +23678,7 @@
         <v>21</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>89</v>
@@ -23708,13 +23706,13 @@
         <v>84</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J194" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K194" t="s" s="2">
         <v>705</v>
@@ -23929,7 +23927,7 @@
         <v>21</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L196" t="s" s="2">
         <v>132</v>
@@ -23976,19 +23974,19 @@
         <v>21</v>
       </c>
       <c r="AB196" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC196" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD196" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE196" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>76</v>
@@ -24000,7 +23998,7 @@
         <v>21</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK196" t="s" s="2">
         <v>89</v>
@@ -24028,13 +24026,13 @@
         <v>84</v>
       </c>
       <c r="H197" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I197" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J197" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K197" t="s" s="2">
         <v>315</v>
@@ -24141,10 +24139,10 @@
         <v>21</v>
       </c>
       <c r="I198" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J198" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K198" t="s" s="2">
         <v>169</v>
@@ -24248,13 +24246,13 @@
         <v>84</v>
       </c>
       <c r="H199" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I199" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J199" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K199" t="s" s="2">
         <v>85</v>
@@ -24356,13 +24354,13 @@
         <v>84</v>
       </c>
       <c r="H200" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I200" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K200" t="s" s="2">
         <v>110</v>
@@ -24464,13 +24462,13 @@
         <v>84</v>
       </c>
       <c r="H201" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I201" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J201" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K201" t="s" s="2">
         <v>169</v>
@@ -24574,13 +24572,13 @@
         <v>84</v>
       </c>
       <c r="H202" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I202" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J202" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K202" t="s" s="2">
         <v>705</v>
@@ -24795,7 +24793,7 @@
         <v>21</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L204" t="s" s="2">
         <v>132</v>
@@ -24842,19 +24840,19 @@
         <v>21</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC204" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD204" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE204" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>76</v>
@@ -24866,7 +24864,7 @@
         <v>21</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>89</v>
@@ -24894,13 +24892,13 @@
         <v>84</v>
       </c>
       <c r="H205" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I205" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J205" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K205" t="s" s="2">
         <v>315</v>
@@ -25007,10 +25005,10 @@
         <v>21</v>
       </c>
       <c r="I206" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J206" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K206" t="s" s="2">
         <v>169</v>
@@ -25114,13 +25112,13 @@
         <v>84</v>
       </c>
       <c r="H207" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I207" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J207" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K207" t="s" s="2">
         <v>85</v>
@@ -25222,13 +25220,13 @@
         <v>84</v>
       </c>
       <c r="H208" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I208" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J208" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K208" t="s" s="2">
         <v>110</v>
@@ -25330,13 +25328,13 @@
         <v>84</v>
       </c>
       <c r="H209" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I209" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K209" t="s" s="2">
         <v>169</v>
@@ -25440,13 +25438,13 @@
         <v>84</v>
       </c>
       <c r="H210" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I210" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K210" t="s" s="2">
         <v>700</v>
@@ -25665,7 +25663,7 @@
         <v>21</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L212" t="s" s="2">
         <v>132</v>
@@ -25712,19 +25710,19 @@
         <v>21</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC212" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD212" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>76</v>
@@ -25736,7 +25734,7 @@
         <v>21</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>89</v>
@@ -25764,13 +25762,13 @@
         <v>84</v>
       </c>
       <c r="H213" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I213" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K213" t="s" s="2">
         <v>705</v>
@@ -25985,7 +25983,7 @@
         <v>21</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L215" t="s" s="2">
         <v>132</v>
@@ -26032,19 +26030,19 @@
         <v>21</v>
       </c>
       <c r="AB215" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC215" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD215" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE215" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>76</v>
@@ -26056,7 +26054,7 @@
         <v>21</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>89</v>
@@ -26084,13 +26082,13 @@
         <v>84</v>
       </c>
       <c r="H216" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I216" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K216" t="s" s="2">
         <v>315</v>
@@ -26197,10 +26195,10 @@
         <v>21</v>
       </c>
       <c r="I217" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J217" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K217" t="s" s="2">
         <v>169</v>
@@ -26304,13 +26302,13 @@
         <v>84</v>
       </c>
       <c r="H218" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I218" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J218" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K218" t="s" s="2">
         <v>85</v>
@@ -26412,13 +26410,13 @@
         <v>84</v>
       </c>
       <c r="H219" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I219" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K219" t="s" s="2">
         <v>110</v>
@@ -26520,13 +26518,13 @@
         <v>84</v>
       </c>
       <c r="H220" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I220" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K220" t="s" s="2">
         <v>169</v>
@@ -26630,13 +26628,13 @@
         <v>84</v>
       </c>
       <c r="H221" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I221" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J221" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K221" t="s" s="2">
         <v>705</v>
@@ -26851,7 +26849,7 @@
         <v>21</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L223" t="s" s="2">
         <v>132</v>
@@ -26898,19 +26896,19 @@
         <v>21</v>
       </c>
       <c r="AB223" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC223" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD223" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE223" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>76</v>
@@ -26922,7 +26920,7 @@
         <v>21</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK223" t="s" s="2">
         <v>89</v>
@@ -26950,13 +26948,13 @@
         <v>84</v>
       </c>
       <c r="H224" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I224" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J224" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K224" t="s" s="2">
         <v>315</v>
@@ -27063,10 +27061,10 @@
         <v>21</v>
       </c>
       <c r="I225" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J225" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K225" t="s" s="2">
         <v>169</v>
@@ -27170,13 +27168,13 @@
         <v>84</v>
       </c>
       <c r="H226" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I226" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J226" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K226" t="s" s="2">
         <v>85</v>
@@ -27278,13 +27276,13 @@
         <v>84</v>
       </c>
       <c r="H227" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I227" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K227" t="s" s="2">
         <v>110</v>
@@ -27386,13 +27384,13 @@
         <v>84</v>
       </c>
       <c r="H228" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I228" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J228" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K228" t="s" s="2">
         <v>169</v>
@@ -27496,13 +27494,13 @@
         <v>84</v>
       </c>
       <c r="H229" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I229" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J229" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K229" t="s" s="2">
         <v>364</v>
@@ -27721,7 +27719,7 @@
         <v>21</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L231" t="s" s="2">
         <v>132</v>
@@ -27768,19 +27766,19 @@
         <v>21</v>
       </c>
       <c r="AB231" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC231" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD231" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE231" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>76</v>
@@ -27792,7 +27790,7 @@
         <v>21</v>
       </c>
       <c r="AJ231" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK231" t="s" s="2">
         <v>89</v>
@@ -27820,13 +27818,13 @@
         <v>84</v>
       </c>
       <c r="H232" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I232" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J232" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K232" t="s" s="2">
         <v>315</v>
@@ -27933,10 +27931,10 @@
         <v>21</v>
       </c>
       <c r="I233" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J233" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K233" t="s" s="2">
         <v>169</v>
@@ -28040,13 +28038,13 @@
         <v>84</v>
       </c>
       <c r="H234" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I234" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J234" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K234" t="s" s="2">
         <v>85</v>
@@ -28148,13 +28146,13 @@
         <v>84</v>
       </c>
       <c r="H235" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I235" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J235" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K235" t="s" s="2">
         <v>110</v>
@@ -28256,13 +28254,13 @@
         <v>84</v>
       </c>
       <c r="H236" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I236" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J236" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K236" t="s" s="2">
         <v>169</v>
@@ -28366,13 +28364,13 @@
         <v>84</v>
       </c>
       <c r="H237" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I237" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J237" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K237" t="s" s="2">
         <v>364</v>
@@ -28589,7 +28587,7 @@
         <v>21</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L239" t="s" s="2">
         <v>132</v>
@@ -28636,19 +28634,19 @@
         <v>21</v>
       </c>
       <c r="AB239" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC239" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD239" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE239" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>76</v>
@@ -28660,7 +28658,7 @@
         <v>21</v>
       </c>
       <c r="AJ239" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK239" t="s" s="2">
         <v>89</v>
@@ -28688,13 +28686,13 @@
         <v>84</v>
       </c>
       <c r="H240" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I240" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J240" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K240" t="s" s="2">
         <v>315</v>
@@ -28801,10 +28799,10 @@
         <v>21</v>
       </c>
       <c r="I241" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J241" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K241" t="s" s="2">
         <v>169</v>
@@ -28908,13 +28906,13 @@
         <v>84</v>
       </c>
       <c r="H242" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I242" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J242" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K242" t="s" s="2">
         <v>85</v>
@@ -29016,13 +29014,13 @@
         <v>84</v>
       </c>
       <c r="H243" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I243" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J243" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K243" t="s" s="2">
         <v>110</v>
@@ -29124,13 +29122,13 @@
         <v>84</v>
       </c>
       <c r="H244" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I244" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J244" t="s" s="2">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="K244" t="s" s="2">
         <v>169</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -399,7 +399,7 @@
     <t>Code für die Art der Dosierung</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetDosageCategory</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-dosagecategory-vs</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -495,7 +495,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/AtElgaEmedCodeSystemDosageCategory</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/at-elga-emed-codesystem-dosagecategory-cs</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1480,7 +1480,7 @@
     <t>Timings are frequently determined by occurrences such as waking, eating and sleep.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaTimingWhenStandardAdministrationVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-timingwhenstandardadministration-vs</t>
   </si>
   <si>
     <t>Timing.repeat.when</t>
@@ -2789,7 +2789,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.35546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="81.67578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8364" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8364" uniqueCount="794">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -623,7 +623,7 @@
     <t>Dosage.extension.value[x].text</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>Plain text representation of the concept</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1021,6 +1021,9 @@
     <t>Dosage.timing.repeat.bounds[x].comparator</t>
   </si>
   <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
     <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
   </si>
   <si>
@@ -1613,6 +1616,9 @@
     <t>Dosage.site.text</t>
   </si>
   <si>
+    <t>Fachliche Begründung: TODO</t>
+  </si>
+  <si>
     <t>Dosage.route</t>
   </si>
   <si>
@@ -1845,9 +1851,6 @@
     <t>Dosage.doseAndRate.dose[x].low.comparator</t>
   </si>
   <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
     <t>Dosage.doseAndRate.dose[x]:doseRange.low.unit</t>
   </si>
   <si>
@@ -1924,7 +1927,7 @@
 </t>
   </si>
   <si>
-    <t>TODO</t>
+    <t>Amount of medication per dose</t>
   </si>
   <si>
     <t>https://termgit.elga.gv.at/ValueSet/elga-medikationmengenart</t>
@@ -8768,20 +8771,20 @@
         <v>169</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q56" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R56" t="s" s="2">
         <v>21</v>
@@ -8805,10 +8808,10 @@
         <v>122</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>21</v>
@@ -8826,7 +8829,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8841,18 +8844,18 @@
         <v>126</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8878,14 +8881,14 @@
         <v>85</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8934,7 +8937,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8949,18 +8952,18 @@
         <v>126</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8986,14 +8989,14 @@
         <v>110</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -9042,7 +9045,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -9051,24 +9054,24 @@
         <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9094,16 +9097,16 @@
         <v>169</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9152,7 +9155,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9167,21 +9170,21 @@
         <v>126</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>275</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>21</v>
@@ -9203,7 +9206,7 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>277</v>
@@ -9283,7 +9286,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>287</v>
@@ -9389,7 +9392,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>289</v>
@@ -9497,10 +9500,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9523,16 +9526,16 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9582,7 +9585,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9594,21 +9597,21 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>297</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9711,10 +9714,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9819,10 +9822,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9929,10 +9932,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9958,20 +9961,20 @@
         <v>169</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q67" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R67" t="s" s="2">
         <v>21</v>
@@ -9995,10 +9998,10 @@
         <v>122</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>21</v>
@@ -10016,7 +10019,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10031,18 +10034,18 @@
         <v>126</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10068,14 +10071,14 @@
         <v>85</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10124,7 +10127,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10139,18 +10142,18 @@
         <v>126</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10176,14 +10179,14 @@
         <v>110</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -10232,7 +10235,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10241,24 +10244,24 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10284,16 +10287,16 @@
         <v>169</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10342,7 +10345,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10357,18 +10360,18 @@
         <v>126</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10391,16 +10394,16 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10450,7 +10453,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10462,21 +10465,21 @@
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>306</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10579,10 +10582,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10687,10 +10690,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10797,10 +10800,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10826,20 +10829,20 @@
         <v>169</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q75" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R75" t="s" s="2">
         <v>21</v>
@@ -10863,10 +10866,10 @@
         <v>122</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -10884,7 +10887,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10899,18 +10902,18 @@
         <v>126</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10936,14 +10939,14 @@
         <v>85</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10992,7 +10995,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11007,18 +11010,18 @@
         <v>126</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11044,14 +11047,14 @@
         <v>110</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -11100,7 +11103,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11109,24 +11112,24 @@
         <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11152,16 +11155,16 @@
         <v>169</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -11210,7 +11213,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11225,18 +11228,18 @@
         <v>126</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11259,19 +11262,19 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -11320,7 +11323,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11335,7 +11338,7 @@
         <v>126</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>21</v>
@@ -11343,10 +11346,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11369,13 +11372,13 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11426,7 +11429,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11441,7 +11444,7 @@
         <v>126</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>21</v>
@@ -11449,10 +11452,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11478,16 +11481,16 @@
         <v>315</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -11536,7 +11539,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11551,7 +11554,7 @@
         <v>126</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>21</v>
@@ -11559,10 +11562,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11588,16 +11591,16 @@
         <v>315</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11646,7 +11649,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11661,7 +11664,7 @@
         <v>126</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>21</v>
@@ -11669,10 +11672,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11698,10 +11701,10 @@
         <v>169</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11731,10 +11734,10 @@
         <v>122</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>21</v>
@@ -11752,7 +11755,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11767,7 +11770,7 @@
         <v>126</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>21</v>
@@ -11775,10 +11778,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11801,13 +11804,13 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11815,7 +11818,7 @@
         <v>21</v>
       </c>
       <c r="Q84" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="R84" t="s" s="2">
         <v>21</v>
@@ -11860,7 +11863,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -11875,7 +11878,7 @@
         <v>126</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>21</v>
@@ -11883,10 +11886,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11909,13 +11912,13 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11966,7 +11969,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11981,7 +11984,7 @@
         <v>126</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>21</v>
@@ -11989,10 +11992,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12018,10 +12021,10 @@
         <v>315</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12072,7 +12075,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12087,7 +12090,7 @@
         <v>126</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>21</v>
@@ -12095,10 +12098,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12124,10 +12127,10 @@
         <v>315</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12178,7 +12181,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12193,7 +12196,7 @@
         <v>126</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>21</v>
@@ -12201,10 +12204,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12230,10 +12233,10 @@
         <v>169</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12264,7 +12267,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>21</v>
@@ -12282,7 +12285,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12297,7 +12300,7 @@
         <v>126</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>21</v>
@@ -12305,10 +12308,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12334,13 +12337,13 @@
         <v>169</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12370,7 +12373,7 @@
       </c>
       <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>21</v>
@@ -12388,7 +12391,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12411,10 +12414,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12437,16 +12440,16 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12496,7 +12499,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12519,10 +12522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12548,16 +12551,16 @@
         <v>169</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -12586,7 +12589,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>21</v>
@@ -12604,7 +12607,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12619,7 +12622,7 @@
         <v>126</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>21</v>
@@ -12627,10 +12630,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12653,13 +12656,13 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12710,7 +12713,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12725,7 +12728,7 @@
         <v>126</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>21</v>
@@ -12733,10 +12736,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12762,13 +12765,13 @@
         <v>119</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12794,13 +12797,13 @@
         <v>21</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>21</v>
@@ -12818,7 +12821,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12833,7 +12836,7 @@
         <v>126</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>21</v>
@@ -12841,10 +12844,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12870,13 +12873,13 @@
         <v>187</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12926,7 +12929,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12941,18 +12944,18 @@
         <v>126</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12978,16 +12981,16 @@
         <v>119</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>21</v>
@@ -13015,10 +13018,10 @@
         <v>224</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>21</v>
@@ -13036,7 +13039,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13051,18 +13054,18 @@
         <v>126</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13165,10 +13168,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13273,10 +13276,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13383,10 +13386,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13489,10 +13492,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13597,10 +13600,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13707,10 +13710,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13815,10 +13818,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13923,10 +13926,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14031,10 +14034,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14141,10 +14144,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14170,7 +14173,7 @@
         <v>85</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>197</v>
+        <v>521</v>
       </c>
       <c r="M106" t="s" s="2">
         <v>198</v>
@@ -14251,10 +14254,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14280,14 +14283,14 @@
         <v>119</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -14315,10 +14318,10 @@
         <v>224</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>21</v>
@@ -14336,7 +14339,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14351,18 +14354,18 @@
         <v>126</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14465,10 +14468,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14573,10 +14576,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14683,10 +14686,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14789,10 +14792,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14897,10 +14900,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14945,7 +14948,7 @@
         <v>21</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>21</v>
@@ -15007,10 +15010,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15115,10 +15118,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15223,10 +15226,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15331,10 +15334,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15441,10 +15444,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15470,7 +15473,7 @@
         <v>85</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>197</v>
+        <v>521</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>198</v>
@@ -15551,10 +15554,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15580,16 +15583,16 @@
         <v>119</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>21</v>
@@ -15617,10 +15620,10 @@
         <v>224</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>21</v>
@@ -15638,7 +15641,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -15653,18 +15656,18 @@
         <v>126</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15767,10 +15770,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15875,10 +15878,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15985,10 +15988,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16091,10 +16094,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16199,10 +16202,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16309,10 +16312,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16417,10 +16420,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16525,10 +16528,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16633,10 +16636,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16743,10 +16746,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16772,7 +16775,7 @@
         <v>85</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>197</v>
+        <v>521</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>198</v>
@@ -16853,10 +16856,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16882,10 +16885,10 @@
         <v>260</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -16936,7 +16939,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -16954,15 +16957,15 @@
         <v>21</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17065,10 +17068,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17173,10 +17176,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17202,14 +17205,14 @@
         <v>119</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>21</v>
@@ -17237,10 +17240,10 @@
         <v>224</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>21</v>
@@ -17258,7 +17261,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17276,15 +17279,15 @@
         <v>21</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17307,19 +17310,19 @@
         <v>91</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>21</v>
@@ -17366,7 +17369,7 @@
         <v>280</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17381,21 +17384,21 @@
         <v>126</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>21</v>
@@ -17417,19 +17420,19 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>21</v>
@@ -17478,7 +17481,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -17493,18 +17496,18 @@
         <v>126</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17607,10 +17610,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17715,10 +17718,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17741,16 +17744,16 @@
         <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -17800,7 +17803,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -17812,21 +17815,21 @@
         <v>21</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>297</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17929,10 +17932,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18037,10 +18040,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18147,10 +18150,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18176,20 +18179,20 @@
         <v>169</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>597</v>
+        <v>325</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q143" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R143" t="s" s="2">
         <v>21</v>
@@ -18213,10 +18216,10 @@
         <v>122</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>21</v>
@@ -18234,7 +18237,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
@@ -18249,18 +18252,18 @@
         <v>126</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18286,14 +18289,14 @@
         <v>85</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>21</v>
@@ -18342,7 +18345,7 @@
         <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
@@ -18357,18 +18360,18 @@
         <v>126</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18394,14 +18397,14 @@
         <v>110</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>21</v>
@@ -18450,7 +18453,7 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
@@ -18459,24 +18462,24 @@
         <v>84</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18502,16 +18505,16 @@
         <v>169</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>21</v>
@@ -18560,7 +18563,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -18575,18 +18578,18 @@
         <v>126</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18609,16 +18612,16 @@
         <v>91</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -18668,7 +18671,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -18680,21 +18683,21 @@
         <v>21</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>306</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18797,10 +18800,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18905,10 +18908,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19015,10 +19018,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19044,20 +19047,20 @@
         <v>169</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>597</v>
+        <v>325</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q151" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R151" t="s" s="2">
         <v>21</v>
@@ -19081,10 +19084,10 @@
         <v>122</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>21</v>
@@ -19102,7 +19105,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
@@ -19117,18 +19120,18 @@
         <v>126</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19154,14 +19157,14 @@
         <v>85</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>21</v>
@@ -19210,7 +19213,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>76</v>
@@ -19225,18 +19228,18 @@
         <v>126</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19262,14 +19265,14 @@
         <v>110</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>21</v>
@@ -19318,7 +19321,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
@@ -19327,24 +19330,24 @@
         <v>84</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19370,16 +19373,16 @@
         <v>169</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>21</v>
@@ -19428,7 +19431,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -19443,21 +19446,21 @@
         <v>126</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D155" t="s" s="2">
         <v>21</v>
@@ -19479,19 +19482,19 @@
         <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>21</v>
@@ -19520,7 +19523,7 @@
       </c>
       <c r="Y155" s="2"/>
       <c r="Z155" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>21</v>
@@ -19538,7 +19541,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
@@ -19553,18 +19556,18 @@
         <v>126</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19667,10 +19670,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19775,10 +19778,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19885,10 +19888,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19914,20 +19917,20 @@
         <v>169</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>597</v>
+        <v>325</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q159" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R159" t="s" s="2">
         <v>21</v>
@@ -19951,10 +19954,10 @@
         <v>122</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>21</v>
@@ -19972,7 +19975,7 @@
         <v>21</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -19987,18 +19990,18 @@
         <v>126</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20024,14 +20027,14 @@
         <v>85</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>21</v>
@@ -20080,7 +20083,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -20095,18 +20098,18 @@
         <v>126</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20132,14 +20135,14 @@
         <v>110</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>21</v>
@@ -20188,7 +20191,7 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -20197,24 +20200,24 @@
         <v>84</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20240,16 +20243,16 @@
         <v>169</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>21</v>
@@ -20298,7 +20301,7 @@
         <v>21</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -20313,18 +20316,18 @@
         <v>126</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20347,19 +20350,19 @@
         <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>21</v>
@@ -20406,7 +20409,7 @@
         <v>280</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>76</v>
@@ -20421,21 +20424,21 @@
         <v>126</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>21</v>
@@ -20457,19 +20460,19 @@
         <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>21</v>
@@ -20518,7 +20521,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -20533,18 +20536,18 @@
         <v>126</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20647,10 +20650,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20755,10 +20758,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20865,10 +20868,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -20894,20 +20897,20 @@
         <v>169</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>597</v>
+        <v>325</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q168" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R168" t="s" s="2">
         <v>21</v>
@@ -20931,10 +20934,10 @@
         <v>122</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>21</v>
@@ -20952,7 +20955,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
@@ -20967,18 +20970,18 @@
         <v>126</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21004,14 +21007,14 @@
         <v>85</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>21</v>
@@ -21060,7 +21063,7 @@
         <v>21</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -21075,18 +21078,18 @@
         <v>126</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21112,14 +21115,14 @@
         <v>110</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>21</v>
@@ -21168,7 +21171,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
@@ -21177,24 +21180,24 @@
         <v>84</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21220,16 +21223,16 @@
         <v>169</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>21</v>
@@ -21278,7 +21281,7 @@
         <v>21</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>76</v>
@@ -21293,21 +21296,21 @@
         <v>126</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>21</v>
@@ -21329,19 +21332,19 @@
         <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>21</v>
@@ -21390,7 +21393,7 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>76</v>
@@ -21405,18 +21408,18 @@
         <v>126</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21519,10 +21522,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21627,10 +21630,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -21653,16 +21656,16 @@
         <v>91</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -21712,7 +21715,7 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -21724,21 +21727,21 @@
         <v>21</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>297</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -21841,10 +21844,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -21949,10 +21952,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22059,10 +22062,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22088,20 +22091,20 @@
         <v>169</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>597</v>
+        <v>325</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q179" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R179" t="s" s="2">
         <v>21</v>
@@ -22125,10 +22128,10 @@
         <v>122</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>21</v>
@@ -22146,7 +22149,7 @@
         <v>21</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>76</v>
@@ -22161,18 +22164,18 @@
         <v>126</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22198,14 +22201,14 @@
         <v>85</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>21</v>
@@ -22254,7 +22257,7 @@
         <v>21</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -22269,18 +22272,18 @@
         <v>126</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22306,14 +22309,14 @@
         <v>110</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>21</v>
@@ -22362,7 +22365,7 @@
         <v>21</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -22371,24 +22374,24 @@
         <v>84</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -22414,16 +22417,16 @@
         <v>169</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>21</v>
@@ -22472,7 +22475,7 @@
         <v>21</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -22487,18 +22490,18 @@
         <v>126</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -22521,16 +22524,16 @@
         <v>91</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -22580,7 +22583,7 @@
         <v>21</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
@@ -22592,21 +22595,21 @@
         <v>21</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>306</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -22709,10 +22712,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -22817,10 +22820,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -22927,10 +22930,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -22956,20 +22959,20 @@
         <v>169</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>597</v>
+        <v>325</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q187" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R187" t="s" s="2">
         <v>21</v>
@@ -22993,10 +22996,10 @@
         <v>122</v>
       </c>
       <c r="Y187" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z187" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>21</v>
@@ -23014,7 +23017,7 @@
         <v>21</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>76</v>
@@ -23029,18 +23032,18 @@
         <v>126</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23066,14 +23069,14 @@
         <v>85</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>21</v>
@@ -23122,7 +23125,7 @@
         <v>21</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>76</v>
@@ -23137,18 +23140,18 @@
         <v>126</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23174,14 +23177,14 @@
         <v>110</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>21</v>
@@ -23230,7 +23233,7 @@
         <v>21</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>76</v>
@@ -23239,24 +23242,24 @@
         <v>84</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23282,16 +23285,16 @@
         <v>169</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>21</v>
@@ -23340,7 +23343,7 @@
         <v>21</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>76</v>
@@ -23355,21 +23358,21 @@
         <v>126</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D191" t="s" s="2">
         <v>21</v>
@@ -23391,19 +23394,19 @@
         <v>91</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>21</v>
@@ -23452,7 +23455,7 @@
         <v>21</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>76</v>
@@ -23467,18 +23470,18 @@
         <v>126</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23581,10 +23584,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23689,10 +23692,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -23715,13 +23718,13 @@
         <v>91</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -23772,7 +23775,7 @@
         <v>21</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>76</v>
@@ -23787,7 +23790,7 @@
         <v>126</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>21</v>
@@ -23795,10 +23798,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -23901,10 +23904,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24009,10 +24012,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24119,10 +24122,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24148,20 +24151,20 @@
         <v>169</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q198" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R198" t="s" s="2">
         <v>21</v>
@@ -24185,10 +24188,10 @@
         <v>122</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>21</v>
@@ -24206,7 +24209,7 @@
         <v>21</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>76</v>
@@ -24221,18 +24224,18 @@
         <v>126</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24258,14 +24261,14 @@
         <v>85</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>21</v>
@@ -24314,7 +24317,7 @@
         <v>21</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>76</v>
@@ -24329,18 +24332,18 @@
         <v>126</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24366,14 +24369,14 @@
         <v>110</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>21</v>
@@ -24422,7 +24425,7 @@
         <v>21</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>76</v>
@@ -24431,24 +24434,24 @@
         <v>84</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ200" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24474,16 +24477,16 @@
         <v>169</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>21</v>
@@ -24532,7 +24535,7 @@
         <v>21</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>76</v>
@@ -24547,18 +24550,18 @@
         <v>126</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24581,13 +24584,13 @@
         <v>91</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -24638,7 +24641,7 @@
         <v>21</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>76</v>
@@ -24653,7 +24656,7 @@
         <v>126</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AL202" t="s" s="2">
         <v>21</v>
@@ -24661,10 +24664,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -24767,10 +24770,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -24875,10 +24878,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -24985,10 +24988,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25014,20 +25017,20 @@
         <v>169</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P206" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q206" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R206" t="s" s="2">
         <v>21</v>
@@ -25051,10 +25054,10 @@
         <v>122</v>
       </c>
       <c r="Y206" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z206" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>21</v>
@@ -25072,7 +25075,7 @@
         <v>21</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>76</v>
@@ -25087,18 +25090,18 @@
         <v>126</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -25124,14 +25127,14 @@
         <v>85</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>21</v>
@@ -25180,7 +25183,7 @@
         <v>21</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>76</v>
@@ -25195,18 +25198,18 @@
         <v>126</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25232,14 +25235,14 @@
         <v>110</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>21</v>
@@ -25288,7 +25291,7 @@
         <v>21</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>76</v>
@@ -25297,24 +25300,24 @@
         <v>84</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ208" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25340,16 +25343,16 @@
         <v>169</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>21</v>
@@ -25398,7 +25401,7 @@
         <v>21</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>76</v>
@@ -25413,18 +25416,18 @@
         <v>126</v>
       </c>
       <c r="AK209" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25447,19 +25450,19 @@
         <v>91</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>21</v>
@@ -25508,7 +25511,7 @@
         <v>21</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>76</v>
@@ -25523,18 +25526,18 @@
         <v>126</v>
       </c>
       <c r="AK210" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -25637,10 +25640,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -25745,10 +25748,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -25771,13 +25774,13 @@
         <v>91</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -25828,7 +25831,7 @@
         <v>21</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>76</v>
@@ -25843,7 +25846,7 @@
         <v>126</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>21</v>
@@ -25851,10 +25854,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -25957,10 +25960,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26065,10 +26068,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26175,10 +26178,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26204,20 +26207,20 @@
         <v>169</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q217" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R217" t="s" s="2">
         <v>21</v>
@@ -26241,10 +26244,10 @@
         <v>122</v>
       </c>
       <c r="Y217" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z217" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA217" t="s" s="2">
         <v>21</v>
@@ -26262,7 +26265,7 @@
         <v>21</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>76</v>
@@ -26277,18 +26280,18 @@
         <v>126</v>
       </c>
       <c r="AK217" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL217" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26314,14 +26317,14 @@
         <v>85</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>21</v>
@@ -26370,7 +26373,7 @@
         <v>21</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>76</v>
@@ -26385,18 +26388,18 @@
         <v>126</v>
       </c>
       <c r="AK218" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26422,14 +26425,14 @@
         <v>110</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P219" t="s" s="2">
         <v>21</v>
@@ -26478,7 +26481,7 @@
         <v>21</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>76</v>
@@ -26487,24 +26490,24 @@
         <v>84</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ219" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK219" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL219" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26530,16 +26533,16 @@
         <v>169</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O220" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>21</v>
@@ -26588,7 +26591,7 @@
         <v>21</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>76</v>
@@ -26603,18 +26606,18 @@
         <v>126</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -26637,13 +26640,13 @@
         <v>91</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
@@ -26694,7 +26697,7 @@
         <v>21</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>76</v>
@@ -26709,7 +26712,7 @@
         <v>126</v>
       </c>
       <c r="AK221" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AL221" t="s" s="2">
         <v>21</v>
@@ -26717,10 +26720,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -26823,10 +26826,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -26931,10 +26934,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -27041,10 +27044,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -27070,20 +27073,20 @@
         <v>169</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q225" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R225" t="s" s="2">
         <v>21</v>
@@ -27107,10 +27110,10 @@
         <v>122</v>
       </c>
       <c r="Y225" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z225" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>21</v>
@@ -27128,7 +27131,7 @@
         <v>21</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>76</v>
@@ -27143,18 +27146,18 @@
         <v>126</v>
       </c>
       <c r="AK225" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL225" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -27180,14 +27183,14 @@
         <v>85</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P226" t="s" s="2">
         <v>21</v>
@@ -27236,7 +27239,7 @@
         <v>21</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>76</v>
@@ -27251,18 +27254,18 @@
         <v>126</v>
       </c>
       <c r="AK226" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -27288,14 +27291,14 @@
         <v>110</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>21</v>
@@ -27344,7 +27347,7 @@
         <v>21</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>76</v>
@@ -27353,24 +27356,24 @@
         <v>84</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ227" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK227" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -27396,16 +27399,16 @@
         <v>169</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O228" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>21</v>
@@ -27454,7 +27457,7 @@
         <v>21</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>76</v>
@@ -27469,18 +27472,18 @@
         <v>126</v>
       </c>
       <c r="AK228" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -27503,19 +27506,19 @@
         <v>91</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="O229" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>21</v>
@@ -27564,7 +27567,7 @@
         <v>21</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>76</v>
@@ -27576,10 +27579,10 @@
         <v>21</v>
       </c>
       <c r="AJ229" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK229" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AL229" t="s" s="2">
         <v>21</v>
@@ -27587,10 +27590,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -27693,10 +27696,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -27801,10 +27804,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -27911,10 +27914,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -27940,20 +27943,20 @@
         <v>169</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>597</v>
+        <v>325</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q233" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R233" t="s" s="2">
         <v>21</v>
@@ -27977,10 +27980,10 @@
         <v>122</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>21</v>
@@ -27998,7 +28001,7 @@
         <v>21</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>76</v>
@@ -28013,18 +28016,18 @@
         <v>126</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL233" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -28050,14 +28053,14 @@
         <v>85</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>21</v>
@@ -28106,7 +28109,7 @@
         <v>21</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>76</v>
@@ -28121,18 +28124,18 @@
         <v>126</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL234" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -28158,14 +28161,14 @@
         <v>110</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>21</v>
@@ -28214,7 +28217,7 @@
         <v>21</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>76</v>
@@ -28223,24 +28226,24 @@
         <v>84</v>
       </c>
       <c r="AI235" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ235" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK235" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL235" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -28266,16 +28269,16 @@
         <v>169</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O236" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P236" t="s" s="2">
         <v>21</v>
@@ -28324,7 +28327,7 @@
         <v>21</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>76</v>
@@ -28339,18 +28342,18 @@
         <v>126</v>
       </c>
       <c r="AK236" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL236" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -28373,17 +28376,17 @@
         <v>91</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>21</v>
@@ -28432,7 +28435,7 @@
         <v>21</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>76</v>
@@ -28444,10 +28447,10 @@
         <v>21</v>
       </c>
       <c r="AJ237" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK237" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AL237" t="s" s="2">
         <v>21</v>
@@ -28455,10 +28458,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28561,10 +28564,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -28669,10 +28672,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -28779,10 +28782,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -28808,20 +28811,20 @@
         <v>169</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>597</v>
+        <v>325</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q241" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R241" t="s" s="2">
         <v>21</v>
@@ -28845,10 +28848,10 @@
         <v>122</v>
       </c>
       <c r="Y241" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z241" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>21</v>
@@ -28866,7 +28869,7 @@
         <v>21</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>76</v>
@@ -28881,18 +28884,18 @@
         <v>126</v>
       </c>
       <c r="AK241" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL241" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -28918,14 +28921,14 @@
         <v>85</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>21</v>
@@ -28974,7 +28977,7 @@
         <v>21</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>76</v>
@@ -28989,18 +28992,18 @@
         <v>126</v>
       </c>
       <c r="AK242" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL242" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -29026,14 +29029,14 @@
         <v>110</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>21</v>
@@ -29082,7 +29085,7 @@
         <v>21</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>76</v>
@@ -29091,24 +29094,24 @@
         <v>84</v>
       </c>
       <c r="AI243" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ243" t="s" s="2">
         <v>126</v>
       </c>
       <c r="AK243" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL243" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -29134,16 +29137,16 @@
         <v>169</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O244" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>21</v>
@@ -29192,7 +29195,7 @@
         <v>21</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>76</v>
@@ -29207,10 +29210,10 @@
         <v>126</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL244" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
